--- a/data/13 Week production 2026-10-05.xlsx
+++ b/data/13 Week production 2026-10-05.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alamancefoods-my.sharepoint.com/personal/balapradeepkonda_alamancefoods_com/Documents/Documents/GitHub/Bala_Can_SupplyChain/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_7AC1C4E2D043B0DC69DE6812DE04111471891355" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D86D7E2-DDE6-4BBC-AEF8-DC6CD2461DA7}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_7AC1C4E2D043B0DC69DE6812DE04111471891355" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C04F1F4-C5E2-454D-9DF9-4E333C46E90C}"/>
   <bookViews>
     <workbookView xWindow="11244" yWindow="-17472" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4122,7 +4122,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AS474"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4643,7 +4642,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>65</v>
       </c>
@@ -4778,7 +4777,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>69</v>
       </c>
@@ -4911,7 +4910,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>72</v>
       </c>
@@ -5046,7 +5045,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>75</v>
       </c>
@@ -5179,7 +5178,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>78</v>
       </c>
@@ -5312,7 +5311,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>81</v>
       </c>
@@ -5445,7 +5444,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="12" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>84</v>
       </c>
@@ -5539,28 +5538,28 @@
         <v>0</v>
       </c>
       <c r="AG12" s="15">
-        <v>57246</v>
+        <v>0</v>
       </c>
       <c r="AH12" s="15">
-        <v>13005</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="15">
-        <v>13005</v>
+        <v>0</v>
       </c>
       <c r="AJ12" s="15">
-        <v>9754</v>
+        <v>0</v>
       </c>
       <c r="AK12" s="15">
-        <v>13465</v>
+        <v>0</v>
       </c>
       <c r="AL12" s="15">
-        <v>13465</v>
+        <v>0</v>
       </c>
       <c r="AM12" s="15">
-        <v>13465</v>
+        <v>0</v>
       </c>
       <c r="AN12" s="15">
-        <v>10099</v>
+        <v>0</v>
       </c>
       <c r="AO12" s="15">
         <v>0</v>
@@ -5578,7 +5577,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>87</v>
       </c>
@@ -5713,7 +5712,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>91</v>
       </c>
@@ -5846,7 +5845,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="15" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>94</v>
       </c>
@@ -5979,7 +5978,7 @@
       </c>
       <c r="AS15" s="11"/>
     </row>
-    <row r="16" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>96</v>
       </c>
@@ -6112,7 +6111,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="17" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>99</v>
       </c>
@@ -6245,7 +6244,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>102</v>
       </c>
@@ -6378,7 +6377,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>105</v>
       </c>
@@ -6509,7 +6508,7 @@
       </c>
       <c r="AS19" s="11"/>
     </row>
-    <row r="20" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>107</v>
       </c>
@@ -6640,7 +6639,7 @@
       </c>
       <c r="AS20" s="11"/>
     </row>
-    <row r="21" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>109</v>
       </c>
@@ -6908,7 +6907,7 @@
       </c>
       <c r="AS22" s="11"/>
     </row>
-    <row r="23" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>116</v>
       </c>
@@ -7041,7 +7040,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="24" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>119</v>
       </c>
@@ -7174,7 +7173,7 @@
       </c>
       <c r="AS24" s="11"/>
     </row>
-    <row r="25" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>121</v>
       </c>
@@ -7307,7 +7306,7 @@
       </c>
       <c r="AS25" s="11"/>
     </row>
-    <row r="26" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>123</v>
       </c>
@@ -7440,7 +7439,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="27" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>126</v>
       </c>
@@ -7573,7 +7572,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="28" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>129</v>
       </c>
@@ -7667,28 +7666,28 @@
         <v>0</v>
       </c>
       <c r="AG28" s="15">
-        <v>32265</v>
+        <v>0</v>
       </c>
       <c r="AH28" s="15">
-        <v>9157</v>
+        <v>0</v>
       </c>
       <c r="AI28" s="15">
-        <v>9157</v>
+        <v>0</v>
       </c>
       <c r="AJ28" s="15">
-        <v>6866</v>
+        <v>0</v>
       </c>
       <c r="AK28" s="15">
-        <v>9481</v>
+        <v>0</v>
       </c>
       <c r="AL28" s="15">
-        <v>9481</v>
+        <v>0</v>
       </c>
       <c r="AM28" s="15">
-        <v>9481</v>
+        <v>0</v>
       </c>
       <c r="AN28" s="15">
-        <v>7109</v>
+        <v>0</v>
       </c>
       <c r="AO28" s="15">
         <v>0</v>
@@ -7706,7 +7705,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="29" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>132</v>
       </c>
@@ -7839,7 +7838,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="30" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>135</v>
       </c>
@@ -8107,7 +8106,7 @@
       </c>
       <c r="AS31" s="11"/>
     </row>
-    <row r="32" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>140</v>
       </c>
@@ -8238,7 +8237,7 @@
       </c>
       <c r="AS32" s="11"/>
     </row>
-    <row r="33" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>142</v>
       </c>
@@ -8371,7 +8370,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="34" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>145</v>
       </c>
@@ -8502,7 +8501,7 @@
       </c>
       <c r="AS34" s="11"/>
     </row>
-    <row r="35" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>147</v>
       </c>
@@ -8637,7 +8636,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="36" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>150</v>
       </c>
@@ -8905,7 +8904,7 @@
       </c>
       <c r="AS37" s="11"/>
     </row>
-    <row r="38" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>154</v>
       </c>
@@ -9036,7 +9035,7 @@
       </c>
       <c r="AS38" s="11"/>
     </row>
-    <row r="39" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>156</v>
       </c>
@@ -9304,7 +9303,7 @@
       </c>
       <c r="AS40" s="11"/>
     </row>
-    <row r="41" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>160</v>
       </c>
@@ -9435,7 +9434,7 @@
       </c>
       <c r="AS41" s="11"/>
     </row>
-    <row r="42" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>162</v>
       </c>
@@ -9568,7 +9567,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="43" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>165</v>
       </c>
@@ -9701,7 +9700,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="44" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>168</v>
       </c>
@@ -9969,7 +9968,7 @@
       </c>
       <c r="AS45" s="11"/>
     </row>
-    <row r="46" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>173</v>
       </c>
@@ -10102,7 +10101,7 @@
       </c>
       <c r="AS46" s="11"/>
     </row>
-    <row r="47" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>175</v>
       </c>
@@ -10237,7 +10236,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="48" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>178</v>
       </c>
@@ -10370,7 +10369,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="49" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>181</v>
       </c>
@@ -10503,7 +10502,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="50" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>184</v>
       </c>
@@ -10634,7 +10633,7 @@
       </c>
       <c r="AS50" s="11"/>
     </row>
-    <row r="51" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>186</v>
       </c>
@@ -10765,7 +10764,7 @@
       </c>
       <c r="AS51" s="11"/>
     </row>
-    <row r="52" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>187</v>
       </c>
@@ -10898,7 +10897,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="53" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>190</v>
       </c>
@@ -11164,7 +11163,7 @@
       </c>
       <c r="AS54" s="11"/>
     </row>
-    <row r="55" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>194</v>
       </c>
@@ -11295,7 +11294,7 @@
       </c>
       <c r="AS55" s="11"/>
     </row>
-    <row r="56" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>196</v>
       </c>
@@ -11428,7 +11427,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="57" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>199</v>
       </c>
@@ -11559,7 +11558,7 @@
       </c>
       <c r="AS57" s="11"/>
     </row>
-    <row r="58" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>201</v>
       </c>
@@ -11692,7 +11691,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="59" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>204</v>
       </c>
@@ -11825,7 +11824,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="60" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>207</v>
       </c>
@@ -11958,7 +11957,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="61" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>210</v>
       </c>
@@ -12091,7 +12090,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="62" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>213</v>
       </c>
@@ -12224,7 +12223,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="63" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>216</v>
       </c>
@@ -12357,7 +12356,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="64" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>219</v>
       </c>
@@ -12488,7 +12487,7 @@
       </c>
       <c r="AS64" s="11"/>
     </row>
-    <row r="65" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>221</v>
       </c>
@@ -12621,7 +12620,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="66" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>224</v>
       </c>
@@ -12752,7 +12751,7 @@
       </c>
       <c r="AS66" s="11"/>
     </row>
-    <row r="67" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>226</v>
       </c>
@@ -12885,7 +12884,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="68" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>229</v>
       </c>
@@ -13018,7 +13017,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="69" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>232</v>
       </c>
@@ -13149,7 +13148,7 @@
       </c>
       <c r="AS69" s="11"/>
     </row>
-    <row r="70" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>234</v>
       </c>
@@ -13550,7 +13549,7 @@
       </c>
       <c r="AS72" s="11"/>
     </row>
-    <row r="73" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>240</v>
       </c>
@@ -13683,7 +13682,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="74" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>243</v>
       </c>
@@ -13814,7 +13813,7 @@
       </c>
       <c r="AS74" s="11"/>
     </row>
-    <row r="75" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>245</v>
       </c>
@@ -13947,7 +13946,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="76" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>248</v>
       </c>
@@ -14211,7 +14210,7 @@
       </c>
       <c r="AS77" s="11"/>
     </row>
-    <row r="78" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>252</v>
       </c>
@@ -14342,7 +14341,7 @@
       </c>
       <c r="AS78" s="11"/>
     </row>
-    <row r="79" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>254</v>
       </c>
@@ -14473,7 +14472,7 @@
       </c>
       <c r="AS79" s="11"/>
     </row>
-    <row r="80" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>256</v>
       </c>
@@ -14606,7 +14605,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="81" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>259</v>
       </c>
@@ -14741,7 +14740,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="82" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>262</v>
       </c>
@@ -14874,7 +14873,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="83" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>265</v>
       </c>
@@ -15005,7 +15004,7 @@
       </c>
       <c r="AS83" s="11"/>
     </row>
-    <row r="84" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>267</v>
       </c>
@@ -15136,7 +15135,7 @@
       </c>
       <c r="AS84" s="11"/>
     </row>
-    <row r="85" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>269</v>
       </c>
@@ -15267,7 +15266,7 @@
       </c>
       <c r="AS85" s="11"/>
     </row>
-    <row r="86" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>271</v>
       </c>
@@ -15400,7 +15399,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="87" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>274</v>
       </c>
@@ -15531,7 +15530,7 @@
       </c>
       <c r="AS87" s="11"/>
     </row>
-    <row r="88" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>276</v>
       </c>
@@ -15662,7 +15661,7 @@
       </c>
       <c r="AS88" s="11"/>
     </row>
-    <row r="89" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>278</v>
       </c>
@@ -15793,7 +15792,7 @@
       </c>
       <c r="AS89" s="11"/>
     </row>
-    <row r="90" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>280</v>
       </c>
@@ -15926,7 +15925,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="91" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>283</v>
       </c>
@@ -16192,7 +16191,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="93" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>289</v>
       </c>
@@ -16325,7 +16324,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="94" spans="1:45" ht="49.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:45" ht="49.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>292</v>
       </c>
@@ -16458,7 +16457,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="95" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>295</v>
       </c>
@@ -16591,7 +16590,7 @@
       </c>
       <c r="AS95" s="11"/>
     </row>
-    <row r="96" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>297</v>
       </c>
@@ -16724,7 +16723,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="97" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>300</v>
       </c>
@@ -16857,7 +16856,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="98" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>303</v>
       </c>
@@ -16988,7 +16987,7 @@
       </c>
       <c r="AS98" s="11"/>
     </row>
-    <row r="99" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>305</v>
       </c>
@@ -17119,7 +17118,7 @@
       </c>
       <c r="AS99" s="11"/>
     </row>
-    <row r="100" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>307</v>
       </c>
@@ -17250,7 +17249,7 @@
       </c>
       <c r="AS100" s="11"/>
     </row>
-    <row r="101" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>309</v>
       </c>
@@ -17381,7 +17380,7 @@
       </c>
       <c r="AS101" s="11"/>
     </row>
-    <row r="102" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>311</v>
       </c>
@@ -17512,7 +17511,7 @@
       </c>
       <c r="AS102" s="11"/>
     </row>
-    <row r="103" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>313</v>
       </c>
@@ -17643,7 +17642,7 @@
       </c>
       <c r="AS103" s="11"/>
     </row>
-    <row r="104" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>315</v>
       </c>
@@ -17776,7 +17775,7 @@
       </c>
       <c r="AS104" s="11"/>
     </row>
-    <row r="105" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>317</v>
       </c>
@@ -17907,7 +17906,7 @@
       </c>
       <c r="AS105" s="11"/>
     </row>
-    <row r="106" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>319</v>
       </c>
@@ -18040,7 +18039,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="107" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>322</v>
       </c>
@@ -18173,7 +18172,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="108" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>325</v>
       </c>
@@ -18304,7 +18303,7 @@
       </c>
       <c r="AS108" s="11"/>
     </row>
-    <row r="109" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>327</v>
       </c>
@@ -18437,7 +18436,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="110" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>330</v>
       </c>
@@ -18570,7 +18569,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="111" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>333</v>
       </c>
@@ -18701,7 +18700,7 @@
       </c>
       <c r="AS111" s="11"/>
     </row>
-    <row r="112" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>335</v>
       </c>
@@ -18834,7 +18833,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="113" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>338</v>
       </c>
@@ -18965,7 +18964,7 @@
       </c>
       <c r="AS113" s="11"/>
     </row>
-    <row r="114" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>340</v>
       </c>
@@ -19096,7 +19095,7 @@
       </c>
       <c r="AS114" s="11"/>
     </row>
-    <row r="115" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>342</v>
       </c>
@@ -19227,7 +19226,7 @@
       </c>
       <c r="AS115" s="11"/>
     </row>
-    <row r="116" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>344</v>
       </c>
@@ -19358,7 +19357,7 @@
       </c>
       <c r="AS116" s="11"/>
     </row>
-    <row r="117" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>346</v>
       </c>
@@ -19624,7 +19623,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="119" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>351</v>
       </c>
@@ -19757,7 +19756,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="120" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>354</v>
       </c>
@@ -19890,7 +19889,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="121" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>357</v>
       </c>
@@ -20023,7 +20022,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="122" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>360</v>
       </c>
@@ -20156,7 +20155,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="123" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>363</v>
       </c>
@@ -20287,7 +20286,7 @@
       </c>
       <c r="AS123" s="11"/>
     </row>
-    <row r="124" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>365</v>
       </c>
@@ -20420,7 +20419,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="125" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>368</v>
       </c>
@@ -20553,7 +20552,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="126" spans="1:45" ht="49.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:45" ht="49.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>371</v>
       </c>
@@ -20686,7 +20685,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="127" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>374</v>
       </c>
@@ -20819,7 +20818,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="128" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>377</v>
       </c>
@@ -20950,7 +20949,7 @@
       </c>
       <c r="AS128" s="11"/>
     </row>
-    <row r="129" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>379</v>
       </c>
@@ -21083,7 +21082,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="130" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>382</v>
       </c>
@@ -21216,7 +21215,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="131" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>385</v>
       </c>
@@ -21349,7 +21348,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="132" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>388</v>
       </c>
@@ -21617,7 +21616,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="134" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>394</v>
       </c>
@@ -21750,7 +21749,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="135" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>397</v>
       </c>
@@ -21881,7 +21880,7 @@
       </c>
       <c r="AS135" s="11"/>
     </row>
-    <row r="136" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>399</v>
       </c>
@@ -22012,7 +22011,7 @@
       </c>
       <c r="AS136" s="11"/>
     </row>
-    <row r="137" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>401</v>
       </c>
@@ -22145,7 +22144,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="138" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>404</v>
       </c>
@@ -22276,7 +22275,7 @@
       </c>
       <c r="AS138" s="11"/>
     </row>
-    <row r="139" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>406</v>
       </c>
@@ -22407,7 +22406,7 @@
       </c>
       <c r="AS139" s="11"/>
     </row>
-    <row r="140" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>408</v>
       </c>
@@ -22538,7 +22537,7 @@
       </c>
       <c r="AS140" s="11"/>
     </row>
-    <row r="141" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>410</v>
       </c>
@@ -22671,7 +22670,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="142" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>413</v>
       </c>
@@ -22804,7 +22803,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="143" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>416</v>
       </c>
@@ -22937,7 +22936,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="144" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>419</v>
       </c>
@@ -23070,7 +23069,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="145" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>422</v>
       </c>
@@ -23201,7 +23200,7 @@
       </c>
       <c r="AS145" s="11"/>
     </row>
-    <row r="146" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>424</v>
       </c>
@@ -23334,7 +23333,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="147" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>427</v>
       </c>
@@ -23600,7 +23599,7 @@
       </c>
       <c r="AS148" s="11"/>
     </row>
-    <row r="149" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>432</v>
       </c>
@@ -23733,7 +23732,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="150" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>435</v>
       </c>
@@ -23864,7 +23863,7 @@
       </c>
       <c r="AS150" s="11"/>
     </row>
-    <row r="151" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>437</v>
       </c>
@@ -23997,7 +23996,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="152" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>440</v>
       </c>
@@ -24130,7 +24129,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="153" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>443</v>
       </c>
@@ -24263,7 +24262,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="154" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>446</v>
       </c>
@@ -24396,7 +24395,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="155" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>449</v>
       </c>
@@ -24662,7 +24661,7 @@
       </c>
       <c r="AS156" s="11"/>
     </row>
-    <row r="157" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>455</v>
       </c>
@@ -24795,7 +24794,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="158" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>458</v>
       </c>
@@ -25061,7 +25060,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="160" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>462</v>
       </c>
@@ -25194,7 +25193,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="161" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>464</v>
       </c>
@@ -25325,7 +25324,7 @@
       </c>
       <c r="AS161" s="11"/>
     </row>
-    <row r="162" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>466</v>
       </c>
@@ -25456,7 +25455,7 @@
       </c>
       <c r="AS162" s="11"/>
     </row>
-    <row r="163" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>468</v>
       </c>
@@ -25587,7 +25586,7 @@
       </c>
       <c r="AS163" s="11"/>
     </row>
-    <row r="164" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>470</v>
       </c>
@@ -25718,7 +25717,7 @@
       </c>
       <c r="AS164" s="11"/>
     </row>
-    <row r="165" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>472</v>
       </c>
@@ -25849,7 +25848,7 @@
       </c>
       <c r="AS165" s="11"/>
     </row>
-    <row r="166" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>474</v>
       </c>
@@ -25982,7 +25981,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="167" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>477</v>
       </c>
@@ -26113,7 +26112,7 @@
       </c>
       <c r="AS167" s="11"/>
     </row>
-    <row r="168" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>479</v>
       </c>
@@ -26246,7 +26245,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="169" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
         <v>481</v>
       </c>
@@ -26377,7 +26376,7 @@
       </c>
       <c r="AS169" s="11"/>
     </row>
-    <row r="170" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>483</v>
       </c>
@@ -26508,7 +26507,7 @@
       </c>
       <c r="AS170" s="11"/>
     </row>
-    <row r="171" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>485</v>
       </c>
@@ -26639,7 +26638,7 @@
       </c>
       <c r="AS171" s="11"/>
     </row>
-    <row r="172" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>487</v>
       </c>
@@ -26905,7 +26904,7 @@
       </c>
       <c r="AS173" s="11"/>
     </row>
-    <row r="174" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>492</v>
       </c>
@@ -27036,7 +27035,7 @@
       </c>
       <c r="AS174" s="11"/>
     </row>
-    <row r="175" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>494</v>
       </c>
@@ -27167,7 +27166,7 @@
       </c>
       <c r="AS175" s="11"/>
     </row>
-    <row r="176" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>496</v>
       </c>
@@ -27298,7 +27297,7 @@
       </c>
       <c r="AS176" s="11"/>
     </row>
-    <row r="177" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>498</v>
       </c>
@@ -27431,7 +27430,7 @@
       </c>
       <c r="AS177" s="11"/>
     </row>
-    <row r="178" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>500</v>
       </c>
@@ -27562,7 +27561,7 @@
       </c>
       <c r="AS178" s="11"/>
     </row>
-    <row r="179" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>502</v>
       </c>
@@ -27695,7 +27694,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="180" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>505</v>
       </c>
@@ -27828,7 +27827,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="181" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>508</v>
       </c>
@@ -27959,7 +27958,7 @@
       </c>
       <c r="AS181" s="11"/>
     </row>
-    <row r="182" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
         <v>510</v>
       </c>
@@ -28090,7 +28089,7 @@
       </c>
       <c r="AS182" s="11"/>
     </row>
-    <row r="183" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>512</v>
       </c>
@@ -28221,7 +28220,7 @@
       </c>
       <c r="AS183" s="11"/>
     </row>
-    <row r="184" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>514</v>
       </c>
@@ -28352,7 +28351,7 @@
       </c>
       <c r="AS184" s="11"/>
     </row>
-    <row r="185" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
         <v>516</v>
       </c>
@@ -28483,7 +28482,7 @@
       </c>
       <c r="AS185" s="11"/>
     </row>
-    <row r="186" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>518</v>
       </c>
@@ -28749,7 +28748,7 @@
       </c>
       <c r="AS187" s="11"/>
     </row>
-    <row r="188" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>523</v>
       </c>
@@ -28882,7 +28881,7 @@
       </c>
       <c r="AS188" s="11"/>
     </row>
-    <row r="189" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
         <v>525</v>
       </c>
@@ -29013,7 +29012,7 @@
       </c>
       <c r="AS189" s="11"/>
     </row>
-    <row r="190" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>527</v>
       </c>
@@ -29144,7 +29143,7 @@
       </c>
       <c r="AS190" s="11"/>
     </row>
-    <row r="191" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
         <v>529</v>
       </c>
@@ -29275,7 +29274,7 @@
       </c>
       <c r="AS191" s="11"/>
     </row>
-    <row r="192" spans="1:45" ht="49.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:45" ht="49.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>531</v>
       </c>
@@ -29408,7 +29407,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="193" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>534</v>
       </c>
@@ -29674,7 +29673,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="195" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
         <v>539</v>
       </c>
@@ -29805,7 +29804,7 @@
       </c>
       <c r="AS195" s="11"/>
     </row>
-    <row r="196" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>541</v>
       </c>
@@ -29936,7 +29935,7 @@
       </c>
       <c r="AS196" s="11"/>
     </row>
-    <row r="197" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
         <v>543</v>
       </c>
@@ -30067,7 +30066,7 @@
       </c>
       <c r="AS197" s="11"/>
     </row>
-    <row r="198" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>545</v>
       </c>
@@ -30198,7 +30197,7 @@
       </c>
       <c r="AS198" s="11"/>
     </row>
-    <row r="199" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>547</v>
       </c>
@@ -30331,7 +30330,7 @@
       </c>
       <c r="AS199" s="11"/>
     </row>
-    <row r="200" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>549</v>
       </c>
@@ -30462,7 +30461,7 @@
       </c>
       <c r="AS200" s="11"/>
     </row>
-    <row r="201" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>551</v>
       </c>
@@ -30593,7 +30592,7 @@
       </c>
       <c r="AS201" s="11"/>
     </row>
-    <row r="202" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>553</v>
       </c>
@@ -30724,7 +30723,7 @@
       </c>
       <c r="AS202" s="11"/>
     </row>
-    <row r="203" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
         <v>555</v>
       </c>
@@ -30855,7 +30854,7 @@
       </c>
       <c r="AS203" s="11"/>
     </row>
-    <row r="204" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
         <v>557</v>
       </c>
@@ -30986,7 +30985,7 @@
       </c>
       <c r="AS204" s="11"/>
     </row>
-    <row r="205" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
         <v>559</v>
       </c>
@@ -31117,7 +31116,7 @@
       </c>
       <c r="AS205" s="11"/>
     </row>
-    <row r="206" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
         <v>561</v>
       </c>
@@ -31248,7 +31247,7 @@
       </c>
       <c r="AS206" s="11"/>
     </row>
-    <row r="207" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
         <v>563</v>
       </c>
@@ -31381,7 +31380,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="208" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>566</v>
       </c>
@@ -31512,7 +31511,7 @@
       </c>
       <c r="AS208" s="11"/>
     </row>
-    <row r="209" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
         <v>568</v>
       </c>
@@ -31645,7 +31644,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="210" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>571</v>
       </c>
@@ -31778,7 +31777,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="211" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>574</v>
       </c>
@@ -31909,7 +31908,7 @@
       </c>
       <c r="AS211" s="11"/>
     </row>
-    <row r="212" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>576</v>
       </c>
@@ -32042,7 +32041,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="213" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>578</v>
       </c>
@@ -32173,7 +32172,7 @@
       </c>
       <c r="AS213" s="11"/>
     </row>
-    <row r="214" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>580</v>
       </c>
@@ -32306,7 +32305,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="215" spans="1:45" ht="49.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:45" ht="49.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>583</v>
       </c>
@@ -32439,7 +32438,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="216" spans="1:45" ht="64.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:45" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
         <v>586</v>
       </c>
@@ -32572,7 +32571,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="217" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
         <v>589</v>
       </c>
@@ -32705,7 +32704,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="218" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>592</v>
       </c>
@@ -32836,7 +32835,7 @@
       </c>
       <c r="AS218" s="11"/>
     </row>
-    <row r="219" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
         <v>594</v>
       </c>
@@ -32969,7 +32968,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="220" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
         <v>597</v>
       </c>
@@ -33102,7 +33101,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="221" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
         <v>600</v>
       </c>
@@ -33233,7 +33232,7 @@
       </c>
       <c r="AS221" s="11"/>
     </row>
-    <row r="222" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
         <v>602</v>
       </c>
@@ -33364,7 +33363,7 @@
       </c>
       <c r="AS222" s="11"/>
     </row>
-    <row r="223" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
         <v>604</v>
       </c>
@@ -33497,7 +33496,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="224" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
         <v>607</v>
       </c>
@@ -33630,7 +33629,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="225" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
         <v>610</v>
       </c>
@@ -33896,7 +33895,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="227" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
         <v>615</v>
       </c>
@@ -34029,7 +34028,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="228" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
         <v>618</v>
       </c>
@@ -34162,7 +34161,7 @@
       </c>
       <c r="AS228" s="11"/>
     </row>
-    <row r="229" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
         <v>620</v>
       </c>
@@ -34293,7 +34292,7 @@
       </c>
       <c r="AS229" s="11"/>
     </row>
-    <row r="230" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
         <v>622</v>
       </c>
@@ -34424,7 +34423,7 @@
       </c>
       <c r="AS230" s="11"/>
     </row>
-    <row r="231" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
         <v>624</v>
       </c>
@@ -34690,7 +34689,7 @@
       </c>
       <c r="AS232" s="11"/>
     </row>
-    <row r="233" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A233" s="2" t="s">
         <v>629</v>
       </c>
@@ -34823,7 +34822,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="234" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="s">
         <v>632</v>
       </c>
@@ -34954,7 +34953,7 @@
       </c>
       <c r="AS234" s="11"/>
     </row>
-    <row r="235" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A235" s="2" t="s">
         <v>634</v>
       </c>
@@ -35087,7 +35086,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="236" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A236" s="2" t="s">
         <v>637</v>
       </c>
@@ -35218,7 +35217,7 @@
       </c>
       <c r="AS236" s="11"/>
     </row>
-    <row r="237" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="2" t="s">
         <v>639</v>
       </c>
@@ -35351,7 +35350,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="238" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A238" s="2" t="s">
         <v>642</v>
       </c>
@@ -35615,7 +35614,7 @@
       </c>
       <c r="AS239" s="11"/>
     </row>
-    <row r="240" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A240" s="2" t="s">
         <v>646</v>
       </c>
@@ -35746,7 +35745,7 @@
       </c>
       <c r="AS240" s="11"/>
     </row>
-    <row r="241" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A241" s="2" t="s">
         <v>648</v>
       </c>
@@ -35879,7 +35878,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="242" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="s">
         <v>650</v>
       </c>
@@ -36415,7 +36414,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="246" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A246" s="2" t="s">
         <v>660</v>
       </c>
@@ -36679,7 +36678,7 @@
       </c>
       <c r="AS247" s="11"/>
     </row>
-    <row r="248" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="s">
         <v>664</v>
       </c>
@@ -36812,7 +36811,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="249" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A249" s="2" t="s">
         <v>667</v>
       </c>
@@ -36943,7 +36942,7 @@
       </c>
       <c r="AS249" s="11"/>
     </row>
-    <row r="250" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="s">
         <v>669</v>
       </c>
@@ -37076,7 +37075,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="251" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A251" s="2" t="s">
         <v>672</v>
       </c>
@@ -37209,7 +37208,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="252" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="s">
         <v>675</v>
       </c>
@@ -37342,7 +37341,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="253" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A253" s="2" t="s">
         <v>678</v>
       </c>
@@ -37473,7 +37472,7 @@
       </c>
       <c r="AS253" s="11"/>
     </row>
-    <row r="254" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="2" t="s">
         <v>680</v>
       </c>
@@ -37606,7 +37605,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="255" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A255" s="2" t="s">
         <v>683</v>
       </c>
@@ -37737,7 +37736,7 @@
       </c>
       <c r="AS255" s="11"/>
     </row>
-    <row r="256" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A256" s="2" t="s">
         <v>685</v>
       </c>
@@ -37868,7 +37867,7 @@
       </c>
       <c r="AS256" s="11"/>
     </row>
-    <row r="257" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A257" s="2" t="s">
         <v>687</v>
       </c>
@@ -37999,7 +37998,7 @@
       </c>
       <c r="AS257" s="11"/>
     </row>
-    <row r="258" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A258" s="2" t="s">
         <v>689</v>
       </c>
@@ -38132,7 +38131,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="259" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A259" s="2" t="s">
         <v>692</v>
       </c>
@@ -38263,7 +38262,7 @@
       </c>
       <c r="AS259" s="11"/>
     </row>
-    <row r="260" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A260" s="2" t="s">
         <v>694</v>
       </c>
@@ -38394,7 +38393,7 @@
       </c>
       <c r="AS260" s="11"/>
     </row>
-    <row r="261" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A261" s="2" t="s">
         <v>696</v>
       </c>
@@ -38525,7 +38524,7 @@
       </c>
       <c r="AS261" s="11"/>
     </row>
-    <row r="262" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="2" t="s">
         <v>698</v>
       </c>
@@ -38658,7 +38657,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="263" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="2" t="s">
         <v>701</v>
       </c>
@@ -38791,7 +38790,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="264" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A264" s="2" t="s">
         <v>704</v>
       </c>
@@ -38924,7 +38923,7 @@
       </c>
       <c r="AS264" s="11"/>
     </row>
-    <row r="265" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="2" t="s">
         <v>706</v>
       </c>
@@ -39057,7 +39056,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="266" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A266" s="2" t="s">
         <v>709</v>
       </c>
@@ -39190,7 +39189,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="267" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A267" s="2" t="s">
         <v>712</v>
       </c>
@@ -39321,7 +39320,7 @@
       </c>
       <c r="AS267" s="11"/>
     </row>
-    <row r="268" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A268" s="2" t="s">
         <v>714</v>
       </c>
@@ -39452,7 +39451,7 @@
       </c>
       <c r="AS268" s="11"/>
     </row>
-    <row r="269" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A269" s="2" t="s">
         <v>716</v>
       </c>
@@ -39583,7 +39582,7 @@
       </c>
       <c r="AS269" s="11"/>
     </row>
-    <row r="270" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A270" s="2" t="s">
         <v>718</v>
       </c>
@@ -39714,7 +39713,7 @@
       </c>
       <c r="AS270" s="11"/>
     </row>
-    <row r="271" spans="1:45" ht="49.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:45" ht="49.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="2" t="s">
         <v>720</v>
       </c>
@@ -39847,7 +39846,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="272" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="2" t="s">
         <v>723</v>
       </c>
@@ -39980,7 +39979,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="273" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A273" s="2" t="s">
         <v>726</v>
       </c>
@@ -40111,7 +40110,7 @@
       </c>
       <c r="AS273" s="11"/>
     </row>
-    <row r="274" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A274" s="2" t="s">
         <v>728</v>
       </c>
@@ -40242,7 +40241,7 @@
       </c>
       <c r="AS274" s="11"/>
     </row>
-    <row r="275" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A275" s="2" t="s">
         <v>730</v>
       </c>
@@ -40373,7 +40372,7 @@
       </c>
       <c r="AS275" s="11"/>
     </row>
-    <row r="276" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A276" s="2" t="s">
         <v>731</v>
       </c>
@@ -40506,7 +40505,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="277" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A277" s="2" t="s">
         <v>733</v>
       </c>
@@ -40639,7 +40638,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="278" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="2" t="s">
         <v>736</v>
       </c>
@@ -40772,7 +40771,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="279" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A279" s="2" t="s">
         <v>739</v>
       </c>
@@ -40903,7 +40902,7 @@
       </c>
       <c r="AS279" s="11"/>
     </row>
-    <row r="280" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A280" s="2" t="s">
         <v>741</v>
       </c>
@@ -41034,7 +41033,7 @@
       </c>
       <c r="AS280" s="11"/>
     </row>
-    <row r="281" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="2" t="s">
         <v>743</v>
       </c>
@@ -41167,7 +41166,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="282" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A282" s="2" t="s">
         <v>746</v>
       </c>
@@ -41300,7 +41299,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="283" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A283" s="2" t="s">
         <v>749</v>
       </c>
@@ -41431,7 +41430,7 @@
       </c>
       <c r="AS283" s="11"/>
     </row>
-    <row r="284" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A284" s="2" t="s">
         <v>751</v>
       </c>
@@ -41562,7 +41561,7 @@
       </c>
       <c r="AS284" s="11"/>
     </row>
-    <row r="285" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A285" s="2" t="s">
         <v>753</v>
       </c>
@@ -41693,7 +41692,7 @@
       </c>
       <c r="AS285" s="11"/>
     </row>
-    <row r="286" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A286" s="2" t="s">
         <v>755</v>
       </c>
@@ -41824,7 +41823,7 @@
       </c>
       <c r="AS286" s="11"/>
     </row>
-    <row r="287" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A287" s="2" t="s">
         <v>757</v>
       </c>
@@ -41955,7 +41954,7 @@
       </c>
       <c r="AS287" s="11"/>
     </row>
-    <row r="288" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A288" s="2" t="s">
         <v>759</v>
       </c>
@@ -42086,7 +42085,7 @@
       </c>
       <c r="AS288" s="11"/>
     </row>
-    <row r="289" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A289" s="2" t="s">
         <v>761</v>
       </c>
@@ -42217,7 +42216,7 @@
       </c>
       <c r="AS289" s="11"/>
     </row>
-    <row r="290" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A290" s="2" t="s">
         <v>763</v>
       </c>
@@ -42483,7 +42482,7 @@
       </c>
       <c r="AS291" s="11"/>
     </row>
-    <row r="292" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A292" s="2" t="s">
         <v>768</v>
       </c>
@@ -43017,7 +43016,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="296" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A296" s="2" t="s">
         <v>778</v>
       </c>
@@ -43148,7 +43147,7 @@
       </c>
       <c r="AS296" s="11"/>
     </row>
-    <row r="297" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A297" s="2" t="s">
         <v>780</v>
       </c>
@@ -43281,7 +43280,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="298" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A298" s="2" t="s">
         <v>783</v>
       </c>
@@ -43412,7 +43411,7 @@
       </c>
       <c r="AS298" s="11"/>
     </row>
-    <row r="299" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A299" s="2" t="s">
         <v>785</v>
       </c>
@@ -43545,7 +43544,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="300" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A300" s="2" t="s">
         <v>788</v>
       </c>
@@ -43678,7 +43677,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="301" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A301" s="2" t="s">
         <v>791</v>
       </c>
@@ -43811,7 +43810,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="302" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A302" s="2" t="s">
         <v>794</v>
       </c>
@@ -43944,7 +43943,7 @@
       </c>
       <c r="AS302" s="11"/>
     </row>
-    <row r="303" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A303" s="2" t="s">
         <v>796</v>
       </c>
@@ -44075,7 +44074,7 @@
       </c>
       <c r="AS303" s="11"/>
     </row>
-    <row r="304" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A304" s="2" t="s">
         <v>798</v>
       </c>
@@ -44208,7 +44207,7 @@
       </c>
       <c r="AS304" s="11"/>
     </row>
-    <row r="305" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A305" s="2" t="s">
         <v>800</v>
       </c>
@@ -44474,7 +44473,7 @@
       </c>
       <c r="AS306" s="11"/>
     </row>
-    <row r="307" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A307" s="2" t="s">
         <v>804</v>
       </c>
@@ -44605,7 +44604,7 @@
       </c>
       <c r="AS307" s="11"/>
     </row>
-    <row r="308" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A308" s="2" t="s">
         <v>806</v>
       </c>
@@ -44738,7 +44737,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="309" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A309" s="2" t="s">
         <v>809</v>
       </c>
@@ -44869,7 +44868,7 @@
       </c>
       <c r="AS309" s="11"/>
     </row>
-    <row r="310" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A310" s="2" t="s">
         <v>811</v>
       </c>
@@ -45270,7 +45269,7 @@
       </c>
       <c r="AS312" s="11"/>
     </row>
-    <row r="313" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A313" s="2" t="s">
         <v>817</v>
       </c>
@@ -45401,7 +45400,7 @@
       </c>
       <c r="AS313" s="11"/>
     </row>
-    <row r="314" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A314" s="2" t="s">
         <v>819</v>
       </c>
@@ -45534,7 +45533,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="315" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A315" s="2" t="s">
         <v>822</v>
       </c>
@@ -45665,7 +45664,7 @@
       </c>
       <c r="AS315" s="11"/>
     </row>
-    <row r="316" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A316" s="2" t="s">
         <v>824</v>
       </c>
@@ -45796,7 +45795,7 @@
       </c>
       <c r="AS316" s="11"/>
     </row>
-    <row r="317" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A317" s="2" t="s">
         <v>826</v>
       </c>
@@ -45927,7 +45926,7 @@
       </c>
       <c r="AS317" s="11"/>
     </row>
-    <row r="318" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A318" s="2" t="s">
         <v>828</v>
       </c>
@@ -46060,7 +46059,7 @@
       </c>
       <c r="AS318" s="11"/>
     </row>
-    <row r="319" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A319" s="2" t="s">
         <v>830</v>
       </c>
@@ -46191,7 +46190,7 @@
       </c>
       <c r="AS319" s="11"/>
     </row>
-    <row r="320" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A320" s="2" t="s">
         <v>832</v>
       </c>
@@ -46324,7 +46323,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="321" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A321" s="2" t="s">
         <v>835</v>
       </c>
@@ -46455,7 +46454,7 @@
       </c>
       <c r="AS321" s="11"/>
     </row>
-    <row r="322" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A322" s="2" t="s">
         <v>837</v>
       </c>
@@ -46588,7 +46587,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="323" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A323" s="2" t="s">
         <v>839</v>
       </c>
@@ -46719,7 +46718,7 @@
       </c>
       <c r="AS323" s="11"/>
     </row>
-    <row r="324" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A324" s="2" t="s">
         <v>841</v>
       </c>
@@ -46852,7 +46851,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="325" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A325" s="2" t="s">
         <v>844</v>
       </c>
@@ -46983,7 +46982,7 @@
       </c>
       <c r="AS325" s="11"/>
     </row>
-    <row r="326" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A326" s="2" t="s">
         <v>846</v>
       </c>
@@ -47114,7 +47113,7 @@
       </c>
       <c r="AS326" s="11"/>
     </row>
-    <row r="327" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A327" s="2" t="s">
         <v>848</v>
       </c>
@@ -47247,7 +47246,7 @@
       </c>
       <c r="AS327" s="11"/>
     </row>
-    <row r="328" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A328" s="2" t="s">
         <v>850</v>
       </c>
@@ -47378,7 +47377,7 @@
       </c>
       <c r="AS328" s="11"/>
     </row>
-    <row r="329" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A329" s="2" t="s">
         <v>852</v>
       </c>
@@ -47509,7 +47508,7 @@
       </c>
       <c r="AS329" s="11"/>
     </row>
-    <row r="330" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A330" s="2" t="s">
         <v>854</v>
       </c>
@@ -47640,7 +47639,7 @@
       </c>
       <c r="AS330" s="11"/>
     </row>
-    <row r="331" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A331" s="2" t="s">
         <v>856</v>
       </c>
@@ -47771,7 +47770,7 @@
       </c>
       <c r="AS331" s="11"/>
     </row>
-    <row r="332" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A332" s="2" t="s">
         <v>858</v>
       </c>
@@ -47902,7 +47901,7 @@
       </c>
       <c r="AS332" s="11"/>
     </row>
-    <row r="333" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A333" s="2" t="s">
         <v>860</v>
       </c>
@@ -48033,7 +48032,7 @@
       </c>
       <c r="AS333" s="11"/>
     </row>
-    <row r="334" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A334" s="2" t="s">
         <v>862</v>
       </c>
@@ -48164,7 +48163,7 @@
       </c>
       <c r="AS334" s="11"/>
     </row>
-    <row r="335" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A335" s="2" t="s">
         <v>864</v>
       </c>
@@ -48295,7 +48294,7 @@
       </c>
       <c r="AS335" s="11"/>
     </row>
-    <row r="336" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A336" s="2" t="s">
         <v>866</v>
       </c>
@@ -48426,7 +48425,7 @@
       </c>
       <c r="AS336" s="11"/>
     </row>
-    <row r="337" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A337" s="2" t="s">
         <v>868</v>
       </c>
@@ -48557,7 +48556,7 @@
       </c>
       <c r="AS337" s="11"/>
     </row>
-    <row r="338" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A338" s="2" t="s">
         <v>870</v>
       </c>
@@ -48688,7 +48687,7 @@
       </c>
       <c r="AS338" s="11"/>
     </row>
-    <row r="339" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A339" s="2" t="s">
         <v>872</v>
       </c>
@@ -48821,7 +48820,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="340" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A340" s="2" t="s">
         <v>875</v>
       </c>
@@ -48952,7 +48951,7 @@
       </c>
       <c r="AS340" s="11"/>
     </row>
-    <row r="341" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A341" s="2" t="s">
         <v>877</v>
       </c>
@@ -49085,7 +49084,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="342" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A342" s="2" t="s">
         <v>880</v>
       </c>
@@ -49216,7 +49215,7 @@
       </c>
       <c r="AS342" s="11"/>
     </row>
-    <row r="343" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A343" s="2" t="s">
         <v>882</v>
       </c>
@@ -49349,7 +49348,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="344" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A344" s="2" t="s">
         <v>885</v>
       </c>
@@ -49480,7 +49479,7 @@
       </c>
       <c r="AS344" s="11"/>
     </row>
-    <row r="345" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A345" s="2" t="s">
         <v>887</v>
       </c>
@@ -49611,7 +49610,7 @@
       </c>
       <c r="AS345" s="11"/>
     </row>
-    <row r="346" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A346" s="2" t="s">
         <v>889</v>
       </c>
@@ -49875,7 +49874,7 @@
       </c>
       <c r="AS347" s="11"/>
     </row>
-    <row r="348" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A348" s="2" t="s">
         <v>893</v>
       </c>
@@ -50006,7 +50005,7 @@
       </c>
       <c r="AS348" s="11"/>
     </row>
-    <row r="349" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A349" s="2" t="s">
         <v>895</v>
       </c>
@@ -50137,7 +50136,7 @@
       </c>
       <c r="AS349" s="11"/>
     </row>
-    <row r="350" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A350" s="2" t="s">
         <v>897</v>
       </c>
@@ -50268,7 +50267,7 @@
       </c>
       <c r="AS350" s="11"/>
     </row>
-    <row r="351" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A351" s="2" t="s">
         <v>899</v>
       </c>
@@ -50399,7 +50398,7 @@
       </c>
       <c r="AS351" s="11"/>
     </row>
-    <row r="352" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A352" s="2" t="s">
         <v>901</v>
       </c>
@@ -50532,7 +50531,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="353" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A353" s="2" t="s">
         <v>904</v>
       </c>
@@ -50663,7 +50662,7 @@
       </c>
       <c r="AS353" s="11"/>
     </row>
-    <row r="354" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A354" s="2" t="s">
         <v>906</v>
       </c>
@@ -50794,7 +50793,7 @@
       </c>
       <c r="AS354" s="11"/>
     </row>
-    <row r="355" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A355" s="2" t="s">
         <v>908</v>
       </c>
@@ -50925,7 +50924,7 @@
       </c>
       <c r="AS355" s="11"/>
     </row>
-    <row r="356" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A356" s="2" t="s">
         <v>910</v>
       </c>
@@ -51056,7 +51055,7 @@
       </c>
       <c r="AS356" s="11"/>
     </row>
-    <row r="357" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A357" s="2" t="s">
         <v>912</v>
       </c>
@@ -51187,7 +51186,7 @@
       </c>
       <c r="AS357" s="11"/>
     </row>
-    <row r="358" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A358" s="2" t="s">
         <v>914</v>
       </c>
@@ -51318,7 +51317,7 @@
       </c>
       <c r="AS358" s="11"/>
     </row>
-    <row r="359" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A359" s="2" t="s">
         <v>916</v>
       </c>
@@ -51449,7 +51448,7 @@
       </c>
       <c r="AS359" s="11"/>
     </row>
-    <row r="360" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="2" t="s">
         <v>918</v>
       </c>
@@ -51582,7 +51581,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="361" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A361" s="2" t="s">
         <v>921</v>
       </c>
@@ -51713,7 +51712,7 @@
       </c>
       <c r="AS361" s="11"/>
     </row>
-    <row r="362" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A362" s="2" t="s">
         <v>923</v>
       </c>
@@ -51844,7 +51843,7 @@
       </c>
       <c r="AS362" s="11"/>
     </row>
-    <row r="363" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A363" s="2" t="s">
         <v>925</v>
       </c>
@@ -51975,7 +51974,7 @@
       </c>
       <c r="AS363" s="11"/>
     </row>
-    <row r="364" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A364" s="2" t="s">
         <v>927</v>
       </c>
@@ -52106,7 +52105,7 @@
       </c>
       <c r="AS364" s="11"/>
     </row>
-    <row r="365" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A365" s="2" t="s">
         <v>929</v>
       </c>
@@ -52370,7 +52369,7 @@
       </c>
       <c r="AS366" s="11"/>
     </row>
-    <row r="367" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A367" s="2" t="s">
         <v>933</v>
       </c>
@@ -52501,7 +52500,7 @@
       </c>
       <c r="AS367" s="11"/>
     </row>
-    <row r="368" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A368" s="2" t="s">
         <v>935</v>
       </c>
@@ -52632,7 +52631,7 @@
       </c>
       <c r="AS368" s="11"/>
     </row>
-    <row r="369" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A369" s="2" t="s">
         <v>937</v>
       </c>
@@ -52763,7 +52762,7 @@
       </c>
       <c r="AS369" s="11"/>
     </row>
-    <row r="370" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A370" s="2" t="s">
         <v>939</v>
       </c>
@@ -52894,7 +52893,7 @@
       </c>
       <c r="AS370" s="11"/>
     </row>
-    <row r="371" spans="1:45" ht="79.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:45" ht="79.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="2" t="s">
         <v>941</v>
       </c>
@@ -53027,7 +53026,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="372" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A372" s="2" t="s">
         <v>944</v>
       </c>
@@ -53160,7 +53159,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="373" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A373" s="2" t="s">
         <v>947</v>
       </c>
@@ -53291,7 +53290,7 @@
       </c>
       <c r="AS373" s="11"/>
     </row>
-    <row r="374" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A374" s="2" t="s">
         <v>949</v>
       </c>
@@ -53422,7 +53421,7 @@
       </c>
       <c r="AS374" s="11"/>
     </row>
-    <row r="375" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A375" s="2" t="s">
         <v>951</v>
       </c>
@@ -53553,7 +53552,7 @@
       </c>
       <c r="AS375" s="11"/>
     </row>
-    <row r="376" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A376" s="2" t="s">
         <v>952</v>
       </c>
@@ -53684,7 +53683,7 @@
       </c>
       <c r="AS376" s="11"/>
     </row>
-    <row r="377" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A377" s="2" t="s">
         <v>954</v>
       </c>
@@ -53815,7 +53814,7 @@
       </c>
       <c r="AS377" s="11"/>
     </row>
-    <row r="378" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A378" s="2" t="s">
         <v>956</v>
       </c>
@@ -54079,7 +54078,7 @@
       </c>
       <c r="AS379" s="11"/>
     </row>
-    <row r="380" spans="1:45" ht="34.049999999999997" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:45" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A380" s="2" t="s">
         <v>960</v>
       </c>
@@ -54347,7 +54346,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="382" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A382" s="2" t="s">
         <v>966</v>
       </c>
@@ -54478,7 +54477,7 @@
       </c>
       <c r="AS382" s="11"/>
     </row>
-    <row r="383" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A383" s="2" t="s">
         <v>968</v>
       </c>
@@ -54744,7 +54743,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="385" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A385" s="2" t="s">
         <v>973</v>
       </c>
@@ -54877,7 +54876,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="386" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A386" s="2" t="s">
         <v>976</v>
       </c>
@@ -55008,7 +55007,7 @@
       </c>
       <c r="AS386" s="11"/>
     </row>
-    <row r="387" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A387" s="2" t="s">
         <v>978</v>
       </c>
@@ -55139,7 +55138,7 @@
       </c>
       <c r="AS387" s="11"/>
     </row>
-    <row r="388" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A388" s="2" t="s">
         <v>980</v>
       </c>
@@ -55270,7 +55269,7 @@
       </c>
       <c r="AS388" s="11"/>
     </row>
-    <row r="389" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A389" s="2" t="s">
         <v>982</v>
       </c>
@@ -55403,7 +55402,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="390" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A390" s="2" t="s">
         <v>985</v>
       </c>
@@ -55534,7 +55533,7 @@
       </c>
       <c r="AS390" s="11"/>
     </row>
-    <row r="391" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A391" s="2" t="s">
         <v>987</v>
       </c>
@@ -55665,7 +55664,7 @@
       </c>
       <c r="AS391" s="11"/>
     </row>
-    <row r="392" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A392" s="2" t="s">
         <v>989</v>
       </c>
@@ -55796,7 +55795,7 @@
       </c>
       <c r="AS392" s="11"/>
     </row>
-    <row r="393" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A393" s="2" t="s">
         <v>991</v>
       </c>
@@ -55927,7 +55926,7 @@
       </c>
       <c r="AS393" s="11"/>
     </row>
-    <row r="394" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A394" s="2" t="s">
         <v>993</v>
       </c>
@@ -56058,7 +56057,7 @@
       </c>
       <c r="AS394" s="11"/>
     </row>
-    <row r="395" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A395" s="2" t="s">
         <v>995</v>
       </c>
@@ -56189,7 +56188,7 @@
       </c>
       <c r="AS395" s="11"/>
     </row>
-    <row r="396" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A396" s="2" t="s">
         <v>997</v>
       </c>
@@ -56320,7 +56319,7 @@
       </c>
       <c r="AS396" s="11"/>
     </row>
-    <row r="397" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A397" s="2" t="s">
         <v>999</v>
       </c>
@@ -56451,7 +56450,7 @@
       </c>
       <c r="AS397" s="11"/>
     </row>
-    <row r="398" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A398" s="2" t="s">
         <v>1001</v>
       </c>
@@ -56582,7 +56581,7 @@
       </c>
       <c r="AS398" s="11"/>
     </row>
-    <row r="399" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A399" s="2" t="s">
         <v>1003</v>
       </c>
@@ -56713,7 +56712,7 @@
       </c>
       <c r="AS399" s="11"/>
     </row>
-    <row r="400" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A400" s="2" t="s">
         <v>1005</v>
       </c>
@@ -56844,7 +56843,7 @@
       </c>
       <c r="AS400" s="11"/>
     </row>
-    <row r="401" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A401" s="2" t="s">
         <v>1007</v>
       </c>
@@ -57108,7 +57107,7 @@
       </c>
       <c r="AS402" s="11"/>
     </row>
-    <row r="403" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A403" s="2" t="s">
         <v>1011</v>
       </c>
@@ -57239,7 +57238,7 @@
       </c>
       <c r="AS403" s="11"/>
     </row>
-    <row r="404" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A404" s="2" t="s">
         <v>1013</v>
       </c>
@@ -57370,7 +57369,7 @@
       </c>
       <c r="AS404" s="11"/>
     </row>
-    <row r="405" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A405" s="2" t="s">
         <v>1015</v>
       </c>
@@ -57501,7 +57500,7 @@
       </c>
       <c r="AS405" s="11"/>
     </row>
-    <row r="406" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A406" s="2" t="s">
         <v>1017</v>
       </c>
@@ -57632,7 +57631,7 @@
       </c>
       <c r="AS406" s="11"/>
     </row>
-    <row r="407" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A407" s="2" t="s">
         <v>1019</v>
       </c>
@@ -57763,7 +57762,7 @@
       </c>
       <c r="AS407" s="11"/>
     </row>
-    <row r="408" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A408" s="2" t="s">
         <v>1021</v>
       </c>
@@ -57894,7 +57893,7 @@
       </c>
       <c r="AS408" s="11"/>
     </row>
-    <row r="409" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A409" s="2" t="s">
         <v>1023</v>
       </c>
@@ -58158,7 +58157,7 @@
       </c>
       <c r="AS410" s="11"/>
     </row>
-    <row r="411" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A411" s="2" t="s">
         <v>1027</v>
       </c>
@@ -58289,7 +58288,7 @@
       </c>
       <c r="AS411" s="11"/>
     </row>
-    <row r="412" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A412" s="2" t="s">
         <v>1029</v>
       </c>
@@ -58420,7 +58419,7 @@
       </c>
       <c r="AS412" s="11"/>
     </row>
-    <row r="413" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A413" s="2" t="s">
         <v>1031</v>
       </c>
@@ -58551,7 +58550,7 @@
       </c>
       <c r="AS413" s="11"/>
     </row>
-    <row r="414" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A414" s="2" t="s">
         <v>1033</v>
       </c>
@@ -58682,7 +58681,7 @@
       </c>
       <c r="AS414" s="11"/>
     </row>
-    <row r="415" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A415" s="2" t="s">
         <v>1035</v>
       </c>
@@ -58813,7 +58812,7 @@
       </c>
       <c r="AS415" s="11"/>
     </row>
-    <row r="416" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A416" s="2" t="s">
         <v>1037</v>
       </c>
@@ -58944,7 +58943,7 @@
       </c>
       <c r="AS416" s="11"/>
     </row>
-    <row r="417" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A417" s="2" t="s">
         <v>1039</v>
       </c>
@@ -59075,7 +59074,7 @@
       </c>
       <c r="AS417" s="11"/>
     </row>
-    <row r="418" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A418" s="2" t="s">
         <v>1041</v>
       </c>
@@ -59206,7 +59205,7 @@
       </c>
       <c r="AS418" s="11"/>
     </row>
-    <row r="419" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A419" s="2" t="s">
         <v>1043</v>
       </c>
@@ -59337,7 +59336,7 @@
       </c>
       <c r="AS419" s="11"/>
     </row>
-    <row r="420" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A420" s="2" t="s">
         <v>1045</v>
       </c>
@@ -59468,7 +59467,7 @@
       </c>
       <c r="AS420" s="11"/>
     </row>
-    <row r="421" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A421" s="2" t="s">
         <v>1047</v>
       </c>
@@ -59599,7 +59598,7 @@
       </c>
       <c r="AS421" s="11"/>
     </row>
-    <row r="422" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A422" s="2" t="s">
         <v>1049</v>
       </c>
@@ -59730,7 +59729,7 @@
       </c>
       <c r="AS422" s="11"/>
     </row>
-    <row r="423" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A423" s="2" t="s">
         <v>1051</v>
       </c>
@@ -59861,7 +59860,7 @@
       </c>
       <c r="AS423" s="11"/>
     </row>
-    <row r="424" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A424" s="2" t="s">
         <v>1053</v>
       </c>
@@ -59992,7 +59991,7 @@
       </c>
       <c r="AS424" s="11"/>
     </row>
-    <row r="425" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A425" s="2" t="s">
         <v>1055</v>
       </c>
@@ -60123,7 +60122,7 @@
       </c>
       <c r="AS425" s="11"/>
     </row>
-    <row r="426" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A426" s="2" t="s">
         <v>1057</v>
       </c>
@@ -60254,7 +60253,7 @@
       </c>
       <c r="AS426" s="11"/>
     </row>
-    <row r="427" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A427" s="2" t="s">
         <v>1059</v>
       </c>
@@ -60385,7 +60384,7 @@
       </c>
       <c r="AS427" s="11"/>
     </row>
-    <row r="428" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A428" s="2" t="s">
         <v>1061</v>
       </c>
@@ -60516,7 +60515,7 @@
       </c>
       <c r="AS428" s="11"/>
     </row>
-    <row r="429" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A429" s="2" t="s">
         <v>1063</v>
       </c>
@@ -60647,7 +60646,7 @@
       </c>
       <c r="AS429" s="11"/>
     </row>
-    <row r="430" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A430" s="2" t="s">
         <v>1065</v>
       </c>
@@ -60778,7 +60777,7 @@
       </c>
       <c r="AS430" s="11"/>
     </row>
-    <row r="431" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A431" s="2" t="s">
         <v>1067</v>
       </c>
@@ -60909,7 +60908,7 @@
       </c>
       <c r="AS431" s="11"/>
     </row>
-    <row r="432" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A432" s="2" t="s">
         <v>1069</v>
       </c>
@@ -61040,7 +61039,7 @@
       </c>
       <c r="AS432" s="11"/>
     </row>
-    <row r="433" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A433" s="2" t="s">
         <v>1071</v>
       </c>
@@ -61171,7 +61170,7 @@
       </c>
       <c r="AS433" s="11"/>
     </row>
-    <row r="434" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A434" s="2" t="s">
         <v>1073</v>
       </c>
@@ -61302,7 +61301,7 @@
       </c>
       <c r="AS434" s="11"/>
     </row>
-    <row r="435" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A435" s="2" t="s">
         <v>1075</v>
       </c>
@@ -61433,7 +61432,7 @@
       </c>
       <c r="AS435" s="11"/>
     </row>
-    <row r="436" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A436" s="2" t="s">
         <v>1077</v>
       </c>
@@ -61564,7 +61563,7 @@
       </c>
       <c r="AS436" s="11"/>
     </row>
-    <row r="437" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A437" s="2" t="s">
         <v>1079</v>
       </c>
@@ -61828,7 +61827,7 @@
       </c>
       <c r="AS438" s="11"/>
     </row>
-    <row r="439" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A439" s="2" t="s">
         <v>1083</v>
       </c>
@@ -61959,7 +61958,7 @@
       </c>
       <c r="AS439" s="11"/>
     </row>
-    <row r="440" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A440" s="2" t="s">
         <v>1085</v>
       </c>
@@ -62090,7 +62089,7 @@
       </c>
       <c r="AS440" s="11"/>
     </row>
-    <row r="441" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A441" s="2" t="s">
         <v>1087</v>
       </c>
@@ -62221,7 +62220,7 @@
       </c>
       <c r="AS441" s="11"/>
     </row>
-    <row r="442" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A442" s="2" t="s">
         <v>1089</v>
       </c>
@@ -62352,7 +62351,7 @@
       </c>
       <c r="AS442" s="11"/>
     </row>
-    <row r="443" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A443" s="2" t="s">
         <v>1091</v>
       </c>
@@ -62483,7 +62482,7 @@
       </c>
       <c r="AS443" s="11"/>
     </row>
-    <row r="444" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A444" s="2" t="s">
         <v>1093</v>
       </c>
@@ -62614,7 +62613,7 @@
       </c>
       <c r="AS444" s="11"/>
     </row>
-    <row r="445" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A445" s="2" t="s">
         <v>1095</v>
       </c>
@@ -62745,7 +62744,7 @@
       </c>
       <c r="AS445" s="11"/>
     </row>
-    <row r="446" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A446" s="2" t="s">
         <v>1097</v>
       </c>
@@ -62876,7 +62875,7 @@
       </c>
       <c r="AS446" s="11"/>
     </row>
-    <row r="447" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A447" s="2" t="s">
         <v>1099</v>
       </c>
@@ -63007,7 +63006,7 @@
       </c>
       <c r="AS447" s="11"/>
     </row>
-    <row r="448" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A448" s="2" t="s">
         <v>1101</v>
       </c>
@@ -63138,7 +63137,7 @@
       </c>
       <c r="AS448" s="11"/>
     </row>
-    <row r="449" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A449" s="2" t="s">
         <v>1103</v>
       </c>
@@ -63269,7 +63268,7 @@
       </c>
       <c r="AS449" s="11"/>
     </row>
-    <row r="450" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A450" s="2" t="s">
         <v>1105</v>
       </c>
@@ -63400,7 +63399,7 @@
       </c>
       <c r="AS450" s="11"/>
     </row>
-    <row r="451" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A451" s="2" t="s">
         <v>1107</v>
       </c>
@@ -63531,7 +63530,7 @@
       </c>
       <c r="AS451" s="11"/>
     </row>
-    <row r="452" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A452" s="2" t="s">
         <v>1109</v>
       </c>
@@ -63662,7 +63661,7 @@
       </c>
       <c r="AS452" s="11"/>
     </row>
-    <row r="453" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A453" s="2" t="s">
         <v>1111</v>
       </c>
@@ -63793,7 +63792,7 @@
       </c>
       <c r="AS453" s="11"/>
     </row>
-    <row r="454" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A454" s="2" t="s">
         <v>1113</v>
       </c>
@@ -63924,7 +63923,7 @@
       </c>
       <c r="AS454" s="11"/>
     </row>
-    <row r="455" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A455" s="2" t="s">
         <v>1115</v>
       </c>
@@ -64055,7 +64054,7 @@
       </c>
       <c r="AS455" s="11"/>
     </row>
-    <row r="456" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A456" s="2" t="s">
         <v>1117</v>
       </c>
@@ -64186,7 +64185,7 @@
       </c>
       <c r="AS456" s="11"/>
     </row>
-    <row r="457" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A457" s="2" t="s">
         <v>1119</v>
       </c>
@@ -64317,7 +64316,7 @@
       </c>
       <c r="AS457" s="11"/>
     </row>
-    <row r="458" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A458" s="2" t="s">
         <v>1121</v>
       </c>
@@ -64448,7 +64447,7 @@
       </c>
       <c r="AS458" s="11"/>
     </row>
-    <row r="459" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A459" s="2" t="s">
         <v>1123</v>
       </c>
@@ -64579,7 +64578,7 @@
       </c>
       <c r="AS459" s="11"/>
     </row>
-    <row r="460" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A460" s="2" t="s">
         <v>1125</v>
       </c>
@@ -64710,7 +64709,7 @@
       </c>
       <c r="AS460" s="11"/>
     </row>
-    <row r="461" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A461" s="2" t="s">
         <v>1127</v>
       </c>
@@ -64841,7 +64840,7 @@
       </c>
       <c r="AS461" s="11"/>
     </row>
-    <row r="462" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A462" s="2" t="s">
         <v>1129</v>
       </c>
@@ -64972,7 +64971,7 @@
       </c>
       <c r="AS462" s="11"/>
     </row>
-    <row r="463" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A463" s="2" t="s">
         <v>1131</v>
       </c>
@@ -65103,7 +65102,7 @@
       </c>
       <c r="AS463" s="11"/>
     </row>
-    <row r="464" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A464" s="2" t="s">
         <v>1133</v>
       </c>
@@ -65234,7 +65233,7 @@
       </c>
       <c r="AS464" s="11"/>
     </row>
-    <row r="465" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A465" s="2" t="s">
         <v>1135</v>
       </c>
@@ -65365,7 +65364,7 @@
       </c>
       <c r="AS465" s="11"/>
     </row>
-    <row r="466" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A466" s="2" t="s">
         <v>1137</v>
       </c>
@@ -65496,7 +65495,7 @@
       </c>
       <c r="AS466" s="11"/>
     </row>
-    <row r="467" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A467" s="2" t="s">
         <v>1139</v>
       </c>
@@ -65627,7 +65626,7 @@
       </c>
       <c r="AS467" s="11"/>
     </row>
-    <row r="468" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A468" s="2" t="s">
         <v>1141</v>
       </c>
@@ -65891,7 +65890,7 @@
       </c>
       <c r="AS469" s="11"/>
     </row>
-    <row r="470" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A470" s="2" t="s">
         <v>1145</v>
       </c>
@@ -66022,7 +66021,7 @@
       </c>
       <c r="AS470" s="11"/>
     </row>
-    <row r="471" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A471" s="2" t="s">
         <v>1147</v>
       </c>
@@ -66153,7 +66152,7 @@
       </c>
       <c r="AS471" s="11"/>
     </row>
-    <row r="472" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A472" s="2" t="s">
         <v>1149</v>
       </c>
@@ -66284,7 +66283,7 @@
       </c>
       <c r="AS472" s="11"/>
     </row>
-    <row r="473" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A473" s="2" t="s">
         <v>1151</v>
       </c>
@@ -66415,7 +66414,7 @@
       </c>
       <c r="AS473" s="11"/>
     </row>
-    <row r="474" spans="1:45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A474" s="2" t="s">
         <v>1153</v>
       </c>
@@ -66547,13 +66546,7 @@
       <c r="AS474" s="11"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:AS474" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A5:AS474" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:AS1"/>
     <mergeCell ref="A2:AS2"/>
